--- a/Другое/работа/1. Отчет о проделанной работе/2. Константинова сентябрь.xlsx
+++ b/Другое/работа/1. Отчет о проделанной работе/2. Константинова сентябрь.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="105" windowWidth="15120" windowHeight="8010"/>
@@ -12,7 +12,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">сентябрь!$E$1:$I$71</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="125725"/>
 </workbook>
 </file>
 
@@ -92,9 +92,6 @@
   </si>
   <si>
     <t>Составление служебных записок</t>
-  </si>
-  <si>
-    <t>Проверка сопостовительных ведомостей (отпавшие и дополнительные работы) в рамках проведения технических совещаний, а так же иных смет контрактов</t>
   </si>
   <si>
     <t>Константинова М.В.</t>
@@ -137,15 +134,18 @@
   <si>
     <t>Отчет о проделанной работе за сентябрь</t>
   </si>
+  <si>
+    <t>Проверка сопоставительных ведомостей (отпавшие и дополнительные работы) в рамках проведения технических совещаний, а так же иных смет контрактов</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -391,6 +391,21 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -404,21 +419,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -481,7 +481,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -513,10 +513,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -548,7 +547,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -724,9 +722,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="E1:O71"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="9.140625" style="2"/>
     <col min="5" max="5" width="14.85546875" style="2" customWidth="1"/>
@@ -738,62 +736,62 @@
     <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="5:10" ht="56.25" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="E1" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
+    <row r="1" spans="5:10" ht="56.25" customHeight="1">
+      <c r="E1" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
       <c r="J1" s="22">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="5:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="5:10" ht="45" customHeight="1">
       <c r="E2" s="20" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="5:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="5:10" ht="35.25" customHeight="1">
       <c r="E3" s="20" t="s">
         <v>4</v>
       </c>
       <c r="F3" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="5:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="5:10" ht="39.75" customHeight="1">
       <c r="E4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="31" t="str">
+      <c r="F4" s="36" t="str">
         <f>"с 01 сентября по 28 сентября (" &amp; J1 &amp; " рабочих дней)"</f>
         <v>с 01 сентября по 28 сентября (19 рабочих дней)</v>
       </c>
-      <c r="G4" s="31"/>
+      <c r="G4" s="36"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="5:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="5:10" ht="15.75">
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="5:10" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="5:10" ht="78.75" customHeight="1">
       <c r="E6" s="14" t="s">
         <v>0</v>
       </c>
@@ -810,7 +808,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="5:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="5:10" ht="23.25" customHeight="1">
       <c r="E7" s="5">
         <v>1</v>
       </c>
@@ -828,7 +826,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="5:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="5:10" ht="21.75" customHeight="1">
       <c r="E8" s="5">
         <v>2</v>
       </c>
@@ -846,7 +844,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="5:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="5:10" ht="31.5">
       <c r="E9" s="5">
         <v>3</v>
       </c>
@@ -864,7 +862,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="5:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="5:10" ht="18.75">
       <c r="E10" s="5">
         <v>4</v>
       </c>
@@ -882,7 +880,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="11" spans="5:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="5:10" ht="18.75">
       <c r="E11" s="5">
         <v>5</v>
       </c>
@@ -900,12 +898,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="5:10" ht="63" x14ac:dyDescent="0.25">
+    <row r="12" spans="5:10" ht="63">
       <c r="E12" s="7">
         <v>6</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G12" s="18">
         <v>18</v>
@@ -918,7 +916,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="5:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="5:10" ht="18.75">
       <c r="E13" s="5">
         <v>7</v>
       </c>
@@ -936,7 +934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="5:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="5:10" ht="31.5">
       <c r="E14" s="5">
         <v>8</v>
       </c>
@@ -954,7 +952,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="5:10" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="5:10" ht="18.75" hidden="1">
       <c r="E15" s="5">
         <v>9</v>
       </c>
@@ -966,7 +964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="5:10" ht="18.75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="5:10" ht="18.75" hidden="1">
       <c r="E16" s="5">
         <v>10</v>
       </c>
@@ -978,7 +976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:9" ht="20.25" hidden="1">
       <c r="E17" s="5">
         <v>11</v>
       </c>
@@ -990,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="5:9" ht="20.25" hidden="1">
       <c r="E18" s="5">
         <v>12</v>
       </c>
@@ -1002,7 +1000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="5:9" ht="20.25" hidden="1">
       <c r="E19" s="5">
         <v>13</v>
       </c>
@@ -1014,7 +1012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="5:9" ht="20.25" hidden="1">
       <c r="E20" s="5">
         <v>14</v>
       </c>
@@ -1026,7 +1024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="5:9" ht="20.25" hidden="1">
       <c r="E21" s="5">
         <v>15</v>
       </c>
@@ -1038,7 +1036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="5:9" ht="20.25" hidden="1">
       <c r="E22" s="5">
         <v>16</v>
       </c>
@@ -1050,7 +1048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="5:9" ht="20.25" hidden="1">
       <c r="E23" s="5">
         <v>17</v>
       </c>
@@ -1062,7 +1060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="5:9" ht="20.25" hidden="1">
       <c r="E24" s="5">
         <v>18</v>
       </c>
@@ -1074,7 +1072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="5:9" ht="20.25" hidden="1">
       <c r="E25" s="5">
         <v>19</v>
       </c>
@@ -1086,7 +1084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="5:9" ht="20.25" hidden="1">
       <c r="E26" s="5">
         <v>20</v>
       </c>
@@ -1098,7 +1096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="5:9" ht="20.25" hidden="1">
       <c r="E27" s="5">
         <v>21</v>
       </c>
@@ -1110,7 +1108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="5:9" ht="20.25" hidden="1">
       <c r="E28" s="5">
         <v>22</v>
       </c>
@@ -1122,7 +1120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="5:9" ht="20.25" hidden="1">
       <c r="E29" s="5">
         <v>23</v>
       </c>
@@ -1134,7 +1132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="5:9" ht="20.25" hidden="1">
       <c r="E30" s="5">
         <v>24</v>
       </c>
@@ -1146,7 +1144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="5:9" ht="20.25" hidden="1">
       <c r="E31" s="5">
         <v>25</v>
       </c>
@@ -1158,7 +1156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="5:9" ht="20.25" hidden="1">
       <c r="E32" s="5">
         <v>26</v>
       </c>
@@ -1170,7 +1168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:9" ht="20.25" hidden="1">
       <c r="E33" s="5">
         <v>27</v>
       </c>
@@ -1182,7 +1180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="5:9" ht="20.25" hidden="1">
       <c r="E34" s="5">
         <v>28</v>
       </c>
@@ -1194,7 +1192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:9" ht="20.25" hidden="1">
       <c r="E35" s="5">
         <v>29</v>
       </c>
@@ -1206,7 +1204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:9" ht="20.25" hidden="1">
       <c r="E36" s="5">
         <v>30</v>
       </c>
@@ -1218,7 +1216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:9" ht="20.25" hidden="1">
       <c r="E37" s="5">
         <v>31</v>
       </c>
@@ -1230,7 +1228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="5:9" ht="20.25" hidden="1">
       <c r="E38" s="5">
         <v>32</v>
       </c>
@@ -1242,7 +1240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="5:9" ht="20.25" hidden="1">
       <c r="E39" s="5">
         <v>33</v>
       </c>
@@ -1254,7 +1252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="5:9" ht="20.25" hidden="1">
       <c r="E40" s="5">
         <v>34</v>
       </c>
@@ -1266,7 +1264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="5:9" ht="20.25" hidden="1">
       <c r="E41" s="5">
         <v>35</v>
       </c>
@@ -1278,7 +1276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:9" ht="20.25" hidden="1">
       <c r="E42" s="5">
         <v>36</v>
       </c>
@@ -1290,7 +1288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:9" ht="20.25" hidden="1">
       <c r="E43" s="5">
         <v>37</v>
       </c>
@@ -1302,7 +1300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="5:9" ht="20.25" hidden="1">
       <c r="E44" s="5">
         <v>38</v>
       </c>
@@ -1314,7 +1312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="5:9" ht="20.25" hidden="1">
       <c r="E45" s="5">
         <v>39</v>
       </c>
@@ -1326,7 +1324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="5:9" ht="20.25" hidden="1">
       <c r="E46" s="5">
         <v>40</v>
       </c>
@@ -1338,7 +1336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:9" ht="20.25" hidden="1">
       <c r="E47" s="5">
         <v>41</v>
       </c>
@@ -1350,7 +1348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:9" ht="20.25" hidden="1">
       <c r="E48" s="5">
         <v>42</v>
       </c>
@@ -1362,7 +1360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:9" ht="20.25" hidden="1">
       <c r="E49" s="5">
         <v>43</v>
       </c>
@@ -1374,7 +1372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:9" ht="20.25" hidden="1">
       <c r="E50" s="5">
         <v>44</v>
       </c>
@@ -1386,7 +1384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="5:9" ht="20.25" hidden="1">
       <c r="E51" s="5">
         <v>45</v>
       </c>
@@ -1398,7 +1396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="5:9" ht="20.25" hidden="1">
       <c r="E52" s="5">
         <v>46</v>
       </c>
@@ -1410,7 +1408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="5:9" ht="20.25" hidden="1">
       <c r="E53" s="5">
         <v>47</v>
       </c>
@@ -1422,7 +1420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="5:9" ht="20.25" hidden="1">
       <c r="E54" s="5">
         <v>48</v>
       </c>
@@ -1434,7 +1432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="5:9" ht="20.25" hidden="1">
       <c r="E55" s="5">
         <v>49</v>
       </c>
@@ -1446,7 +1444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="5:9" ht="20.25" hidden="1">
       <c r="E56" s="5">
         <v>50</v>
       </c>
@@ -1458,7 +1456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="5:9" ht="20.25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="5:9" ht="20.25" hidden="1">
       <c r="E57" s="5">
         <v>51</v>
       </c>
@@ -1470,43 +1468,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="5:9">
       <c r="E58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
     </row>
-    <row r="59" spans="5:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="5:9">
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="E60" s="28" t="s">
+    <row r="60" spans="5:9" ht="18.75">
+      <c r="E60" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="28"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="33"/>
+      <c r="H60" s="33"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="5:9" ht="18.75">
       <c r="E61" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="F61" s="29" t="s">
+      <c r="F61" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="G61" s="30"/>
+      <c r="G61" s="35"/>
       <c r="H61" s="11" t="s">
         <v>9</v>
       </c>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="5:9" ht="18.75">
       <c r="E62" s="10">
         <v>1</v>
       </c>
@@ -1520,7 +1518,7 @@
       </c>
       <c r="I62" s="6"/>
     </row>
-    <row r="63" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="5:9" ht="18.75">
       <c r="E63" s="10">
         <v>2</v>
       </c>
@@ -1534,7 +1532,7 @@
       </c>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="5:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="5:9" ht="18.75">
       <c r="E64" s="10">
         <v>3</v>
       </c>
@@ -1548,7 +1546,7 @@
       </c>
       <c r="I64" s="6"/>
     </row>
-    <row r="65" spans="5:15" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="5:15" ht="47.25" customHeight="1">
       <c r="E65" s="10">
         <v>4</v>
       </c>
@@ -1562,7 +1560,7 @@
       </c>
       <c r="I65" s="6"/>
     </row>
-    <row r="66" spans="5:15" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="5:15" ht="18.75">
       <c r="E66" s="10">
         <v>5</v>
       </c>
@@ -1576,49 +1574,49 @@
       </c>
       <c r="I66" s="6"/>
     </row>
-    <row r="67" spans="5:15" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="5:15" ht="18.75">
       <c r="E67" s="10">
         <v>6</v>
       </c>
-      <c r="F67" s="35" t="s">
+      <c r="F67" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="G67" s="36"/>
+      <c r="G67" s="31"/>
       <c r="H67" s="21">
         <f>H66/7</f>
         <v>1.0785714285714285</v>
       </c>
       <c r="I67" s="6"/>
     </row>
-    <row r="68" spans="5:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E68" s="32" t="s">
+    <row r="68" spans="5:15" ht="34.5" customHeight="1">
+      <c r="E68" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="F68" s="32"/>
+      <c r="F68" s="27"/>
       <c r="G68" s="9"/>
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
       <c r="O68" s="12"/>
     </row>
-    <row r="69" spans="5:15" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E69" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="F69" s="33"/>
-      <c r="G69" s="33"/>
-      <c r="H69" s="33"/>
-      <c r="I69" s="33"/>
-    </row>
-    <row r="70" spans="5:15" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E70" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="F70" s="34"/>
+    <row r="69" spans="5:15" ht="81" customHeight="1">
+      <c r="E69" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="28"/>
+    </row>
+    <row r="70" spans="5:15" ht="39" customHeight="1">
+      <c r="E70" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="F70" s="29"/>
       <c r="G70" s="6"/>
       <c r="H70" s="6"/>
       <c r="I70" s="6"/>
     </row>
-    <row r="71" spans="5:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="5:15">
       <c r="E71" s="6"/>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
@@ -1627,12 +1625,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="E69:I69"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="F67:G67"/>
     <mergeCell ref="F64:G64"/>
     <mergeCell ref="E1:I1"/>
     <mergeCell ref="E60:H60"/>
@@ -1640,6 +1632,12 @@
     <mergeCell ref="F62:G62"/>
     <mergeCell ref="F63:G63"/>
     <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="E69:I69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="F67:G67"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="56" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
